--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484168_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484168_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. DE LEON</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5061</v>
+        <v>4.8178</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3069</v>
+        <v>4.416</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1992</v>
+        <v>0.4018</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1268</v>
+        <v>3.2047</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.7107</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5481</v>
+        <v>2.494</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9067</v>
+        <v>4.1131</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.0272</v>
+        <v>1.5026</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1205</v>
+        <v>2.6105</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7799</v>
+        <v>-0.9083</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3523</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4276</v>
+        <v>-0.1165</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>4.034</v>
+        <v>-0.4463</v>
       </c>
       <c r="T2" t="n">
-        <v>3.146</v>
+        <v>0.0965</v>
       </c>
       <c r="U2" t="n">
-        <v>0.888</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4085</v>
+        <v>0.6707</v>
       </c>
       <c r="W2" t="n">
-        <v>0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1425</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>R. DE LEON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7693</v>
+        <v>2.9387</v>
       </c>
       <c r="E3" t="n">
-        <v>4.62</v>
+        <v>0.3286</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1493</v>
+        <v>2.61</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2047</v>
+        <v>-0.1268</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7107</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2.494</v>
+        <v>0.5481</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1131</v>
+        <v>-0.9067</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5026</v>
+        <v>-1.0272</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6105</v>
+        <v>0.1205</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9083</v>
+        <v>0.7799</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.3523</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1165</v>
+        <v>0.4276</v>
       </c>
       <c r="P3" t="n">
+        <v>1.1903</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.1984</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.3887</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.3968</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.7855</v>
-      </c>
       <c r="S3" t="n">
-        <v>-0.4948</v>
+        <v>1.4666</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3005</v>
+        <v>1.1678</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7953</v>
+        <v>0.2989</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6707</v>
+        <v>0.4085</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0675</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6583</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0216</v>
+        <v>0.0839</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6367</v>
+        <v>0.8612</v>
       </c>
       <c r="G4" t="n">
         <v>1.1894</v>
@@ -766,13 +766,13 @@
         <v>2.579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.5101</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0735</v>
+        <v>-0.0112</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.4989</v>
       </c>
       <c r="V4" t="n">
         <v>0.0675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MARTINEZ JANER</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1272</v>
+        <v>0.6201</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0717</v>
+        <v>-1.5003</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1989</v>
+        <v>2.1204</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3797</v>
+        <v>0.3225</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3305</v>
+        <v>1.2903</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0492</v>
+        <v>-0.9678</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.4574</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3321</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5999</v>
+        <v>-1.3954</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4477</v>
+        <v>0.7799</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9983</v>
+        <v>0.3523</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5507</v>
+        <v>0.4276</v>
       </c>
       <c r="P5" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.1903</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.5871</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.1984</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.7855</v>
-      </c>
       <c r="S5" t="n">
-        <v>-1.0169</v>
+        <v>-0.0992</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8105</v>
+        <v>0.1475</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2064</v>
+        <v>-0.2467</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9367</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>B. MARTINEZ JANER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8552999999999999</v>
+        <v>0.4894</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5829</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7276</v>
+        <v>1.255</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3225</v>
+        <v>-1.3797</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2903</v>
+        <v>-1.3305</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9678</v>
+        <v>-0.0492</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4574</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9379999999999999</v>
+        <v>-0.3321</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3954</v>
+        <v>-0.5999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7799</v>
+        <v>-0.4477</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3523</v>
+        <v>-0.9983</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4276</v>
+        <v>0.5507</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5746</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9352</v>
+        <v>-0.5044</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6394</v>
+        <v>-0.1503</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9367</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.156</v>
+        <v>-1.0516</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6069</v>
+        <v>-0.8375</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.549</v>
+        <v>-0.2141</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.628</v>
+        <v>-0.4148</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5541</v>
+        <v>-1.5121</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0738</v>
+        <v>1.0974</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0279</v>
+        <v>0.1034</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.5794</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7229</v>
+        <v>0.6827</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6558</v>
+        <v>-0.5181</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1409</v>
+        <v>-0.9327</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7967</v>
+        <v>0.4146</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0833</v>
+        <v>-0.4223</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4364</v>
+        <v>-0.5441</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.1218</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2065</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3117</v>
+        <v>-1.3626</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0415</v>
+        <v>-0.5049</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2702</v>
+        <v>-0.8576</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4148</v>
+        <v>-0.628</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5121</v>
+        <v>-0.5541</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0974</v>
+        <v>-0.0738</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1034</v>
+        <v>0.0279</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5794</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6827</v>
+        <v>0.7229</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5181</v>
+        <v>-0.6558</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9327</v>
+        <v>0.1409</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4146</v>
+        <v>-0.7967</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6824</v>
+        <v>-0.1233</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7481</v>
+        <v>-0.3344</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.2111</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2065</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3179</v>
+        <v>-2.5821</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.5363</v>
+        <v>-4.576</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2183</v>
+        <v>1.9939</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7592</v>
@@ -1156,13 +1156,13 @@
         <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6949</v>
+        <v>0.4308</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3005</v>
+        <v>0.2608</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3944</v>
+        <v>0.1699</v>
       </c>
       <c r="V9" t="n">
         <v>0.3334</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5741</v>
+        <v>-4.619</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3483</v>
+        <v>-4.6738</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2258</v>
+        <v>0.0548</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4113</v>
@@ -1234,13 +1234,13 @@
         <v>1.5871</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3773</v>
+        <v>-0.4223</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8728</v>
+        <v>-0.1983</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.224</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2065</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1564</v>
+        <v>-6.1947</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7609</v>
+        <v>-5.6588</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3956</v>
+        <v>-0.5359</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3898</v>
@@ -1312,13 +1312,13 @@
         <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1162</v>
+        <v>-0.1545</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3797</v>
+        <v>-0.2776</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2635</v>
+        <v>0.1232</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4763</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.310499999999998</v>
+        <v>-5.9989</v>
       </c>
       <c r="E12" t="n">
-        <v>-14</v>
+        <v>-13.6884</v>
       </c>
       <c r="F12" t="n">
-        <v>7.689400000000001</v>
+        <v>7.689500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-1.393</v>
@@ -1390,13 +1390,13 @@
         <v>16.8627</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.246900000000001</v>
+        <v>-0.9352999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5091999999999999</v>
+        <v>-0.1974</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7376</v>
+        <v>-0.7378</v>
       </c>
       <c r="V12" t="n">
         <v>-2.679</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0131</v>
+        <v>5.4902</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3263</v>
+        <v>2.2242</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6868</v>
+        <v>3.266</v>
       </c>
       <c r="G13" t="n">
         <v>4.2536</v>
@@ -1468,13 +1468,13 @@
         <v>3.1741</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9777</v>
+        <v>0.4548</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3969</v>
+        <v>0.2949</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5808</v>
+        <v>0.16</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4085</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2807</v>
+        <v>3.3751</v>
       </c>
       <c r="E14" t="n">
-        <v>1.536</v>
+        <v>0.2096</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7447</v>
+        <v>3.1655</v>
       </c>
       <c r="G14" t="n">
         <v>-3.366</v>
@@ -1546,13 +1546,13 @@
         <v>2.7774</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2499</v>
+        <v>0.3444</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1314</v>
+        <v>0.805</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8815</v>
+        <v>-0.4606</v>
       </c>
       <c r="V14" t="n">
         <v>3.6194</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1</v>
+        <v>1.9089</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5523</v>
+        <v>0.8381</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5477</v>
+        <v>1.0708</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5767</v>
@@ -1624,13 +1624,13 @@
         <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4108</v>
+        <v>0.2196</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5726</v>
+        <v>-0.1416</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.3612</v>
       </c>
       <c r="V15" t="n">
         <v>1.4724</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0666</v>
+        <v>0.7325</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5715</v>
+        <v>0.2654</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4951</v>
+        <v>0.4671</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0034</v>
@@ -1702,13 +1702,13 @@
         <v>0.5952</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4631</v>
+        <v>0.129</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2438</v>
+        <v>-0.0623</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2193</v>
+        <v>0.1913</v>
       </c>
       <c r="V16" t="n">
         <v>1.0118</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. LOPEZ SAURA</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.136</v>
+        <v>0.4458</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0623</v>
+        <v>-2.8751</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1984</v>
+        <v>3.3209</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.8288</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.8318</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-2.003</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.9686</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2.3239</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.3553</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.1398</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.5079</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1984</v>
+        <v>3.1741</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0623</v>
+        <v>0.1445</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0623</v>
+        <v>-0.408</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.5525</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08989999999999999</v>
+        <v>0.2764</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.6913</v>
+        <v>-0.7891</v>
       </c>
       <c r="F18" t="n">
-        <v>3.6014</v>
+        <v>1.0655</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8288</v>
+        <v>-1.2781</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8318</v>
+        <v>1.0176</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.003</v>
+        <v>-2.2957</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9686</v>
+        <v>-0.8515</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3239</v>
+        <v>0.3884</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3553</v>
+        <v>-1.2399</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1398</v>
+        <v>-0.4265</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5079</v>
+        <v>0.6293</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.0558</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1741</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3912</v>
+        <v>0.1658</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2242</v>
+        <v>0.0624</v>
       </c>
       <c r="U18" t="n">
-        <v>0.833</v>
+        <v>0.1034</v>
       </c>
       <c r="V18" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>M. LOPEZ SAURA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6829</v>
+        <v>0.136</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0887</v>
+        <v>-0.0623</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4057</v>
+        <v>0.1984</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4786</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1057</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5843</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06560000000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0255</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.413</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1312</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5442</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1676</v>
+        <v>-0.0623</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5555</v>
+        <v>-0.0623</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6121</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7005</v>
+        <v>-0.3115</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4013</v>
+        <v>-0.1626</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7008</v>
+        <v>-0.1489</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2781</v>
+        <v>-1.0857</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0176</v>
+        <v>0.2216</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2957</v>
+        <v>-1.3072</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8515</v>
+        <v>-0.5594</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3884</v>
+        <v>0.0806</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2399</v>
+        <v>-0.64</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4265</v>
+        <v>-0.5263</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6293</v>
+        <v>0.1409</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0558</v>
+        <v>-0.6672</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8111</v>
+        <v>0.5838</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5498</v>
+        <v>0.3968</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2614</v>
+        <v>0.187</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>I. FERNANDEZ MASIP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9339</v>
+        <v>-0.5437</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6727</v>
+        <v>-1.6666</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2611</v>
+        <v>1.1228</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0857</v>
+        <v>2.0438</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2216</v>
+        <v>2.474</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3072</v>
+        <v>-0.4302</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5594</v>
+        <v>2.4654</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0806</v>
+        <v>1.9758</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.64</v>
+        <v>0.4896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5263</v>
+        <v>-0.4216</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1409</v>
+        <v>0.4981</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6672</v>
+        <v>-0.9198</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7935</v>
+        <v>-2.7774</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0385</v>
+        <v>-0.4846</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1133</v>
+        <v>-0.1643</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07480000000000001</v>
+        <v>-0.3203</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6032</v>
+        <v>0.6745</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6032</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3578</v>
+        <v>-1.1818</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.98</v>
+        <v>-0.776</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3778</v>
+        <v>-0.4058</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2569</v>
@@ -2170,13 +2170,13 @@
         <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4382</v>
+        <v>-0.2622</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.051</v>
+        <v>0.1531</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3872</v>
+        <v>-0.4152</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MASIP</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5589</v>
+        <v>-1.2696</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1767</v>
+        <v>-2.3947</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6178</v>
+        <v>1.1252</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0438</v>
+        <v>0.4786</v>
       </c>
       <c r="H23" t="n">
-        <v>2.474</v>
+        <v>-0.1057</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4302</v>
+        <v>0.5843</v>
       </c>
       <c r="J23" t="n">
-        <v>2.4654</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9758</v>
+        <v>0.0255</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4896</v>
+        <v>0.0402</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4216</v>
+        <v>0.413</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4981</v>
+        <v>-0.1312</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9198</v>
+        <v>0.5442</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.7774</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9677</v>
+        <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4998</v>
+        <v>0.581</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6744</v>
+        <v>0.2494</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8253</v>
+        <v>0.3315</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6745</v>
+        <v>-0.9405</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6745</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9619</v>
+        <v>-2.7476</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6024</v>
+        <v>-2.5004</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3595</v>
+        <v>-0.2473</v>
       </c>
       <c r="G24" t="n">
         <v>1.3548</v>
@@ -2326,13 +2326,13 @@
         <v>1.5871</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7811</v>
+        <v>-0.5668</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4874</v>
+        <v>-0.3854</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2937</v>
+        <v>-0.1814</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1469</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.310600000000003</v>
+        <v>6.310699999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.689299999999999</v>
+        <v>-7.6895</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>14.0002</v>
       </c>
       <c r="G25" t="n">
         <v>1.392799999999999</v>
@@ -2377,19 +2377,19 @@
         <v>-6.769400000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>3.362799999999999</v>
+        <v>3.3628</v>
       </c>
       <c r="K25" t="n">
         <v>4.238099999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8751999999999998</v>
+        <v>-0.8752000000000002</v>
       </c>
       <c r="M25" t="n">
         <v>-1.9699</v>
       </c>
       <c r="N25" t="n">
-        <v>3.924199999999999</v>
+        <v>3.9242</v>
       </c>
       <c r="O25" t="n">
         <v>-5.8944</v>
@@ -2404,13 +2404,13 @@
         <v>17.8546</v>
       </c>
       <c r="S25" t="n">
-        <v>1.246899999999999</v>
+        <v>1.247</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7378000000000005</v>
+        <v>0.7377000000000002</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5090999999999999</v>
+        <v>0.5094</v>
       </c>
       <c r="V25" t="n">
         <v>2.679</v>
